--- a/data/imlls_database.xlsx
+++ b/data/imlls_database.xlsx
@@ -16561,6 +16561,102 @@
   </si>
   <si>
     <t>То не гаряча чашка.</t>
+  </si>
+  <si>
+    <t>¿Es un gato? - Sí.</t>
+  </si>
+  <si>
+    <t>¿Es una habitación grande? - No.</t>
+  </si>
+  <si>
+    <t>¿Es una buena idea? - Sí.</t>
+  </si>
+  <si>
+    <t>¿Es un piso pequeño? - No.</t>
+  </si>
+  <si>
+    <t>¿Es un libro negro? - Sí.</t>
+  </si>
+  <si>
+    <t>¿Es una mala carretera? - No.</t>
+  </si>
+  <si>
+    <t>¿Es una bolsa roja? - Sí.</t>
+  </si>
+  <si>
+    <t>¿Es un mal día? - No.</t>
+  </si>
+  <si>
+    <t>Це кіт? - Так.</t>
+  </si>
+  <si>
+    <t>Це велика кімната? - Ні.</t>
+  </si>
+  <si>
+    <t>Це гарна ідея? - Так.</t>
+  </si>
+  <si>
+    <t>Це маленька квартира? - Ні.</t>
+  </si>
+  <si>
+    <t>Це чорна книга? - Так.</t>
+  </si>
+  <si>
+    <t>Це погана дорога? - Ні.</t>
+  </si>
+  <si>
+    <t>Це червона сумка? - Так.</t>
+  </si>
+  <si>
+    <t>Це поганий день? - Ні.</t>
+  </si>
+  <si>
+    <t>¿Es este un libro grande? - Sí.</t>
+  </si>
+  <si>
+    <t>¿Es ese un bolígrafo pequeño? - No.</t>
+  </si>
+  <si>
+    <t>¿Es este un vestido negro? - Sí.</t>
+  </si>
+  <si>
+    <t>¿Es ese un sombrero rojo? - No.</t>
+  </si>
+  <si>
+    <t>¿Es esta una buena botella? - Sí.</t>
+  </si>
+  <si>
+    <t>¿Es esa una mala taza? - No.</t>
+  </si>
+  <si>
+    <t>¿Es este un camino nuevo? - Sí.</t>
+  </si>
+  <si>
+    <t>¿Es esa una casa vieja? - No.</t>
+  </si>
+  <si>
+    <t>У тебе є план? - Так.</t>
+  </si>
+  <si>
+    <t>У нас є ідея? - Так.</t>
+  </si>
+  <si>
+    <t>У них є книга? - Ні.</t>
+  </si>
+  <si>
+    <t>У тебе є гаряча чашка? - Так.</t>
+  </si>
+  <si>
+    <t>У нас є холодна пляшка? - Ні.</t>
+  </si>
+  <si>
+    <t>У них є нова квартира? - Так.</t>
+  </si>
+  <si>
+    <t>У тебе є хороша ручка? - Ні.</t>
+  </si>
+  <si>
+    <t>У тебе є великий будинок? - Так.</t>
   </si>
 </sst>
 </file>
@@ -17934,10 +18030,10 @@
         <v>103</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>104</v>
+        <v>5524</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>105</v>
+        <v>5516</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>106</v>
@@ -17976,10 +18072,10 @@
         <v>107</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>108</v>
+        <v>5525</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>109</v>
+        <v>5517</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>110</v>
@@ -18018,10 +18114,10 @@
         <v>111</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>112</v>
+        <v>5526</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>113</v>
+        <v>5518</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>114</v>
@@ -18060,10 +18156,10 @@
         <v>115</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>116</v>
+        <v>5527</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>117</v>
+        <v>5519</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>118</v>
@@ -18102,10 +18198,10 @@
         <v>119</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>120</v>
+        <v>5528</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>121</v>
+        <v>5520</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>122</v>
@@ -18144,10 +18240,10 @@
         <v>123</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>124</v>
+        <v>5529</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>125</v>
+        <v>5521</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>126</v>
@@ -18186,10 +18282,10 @@
         <v>127</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>128</v>
+        <v>5530</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>129</v>
+        <v>5522</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>130</v>
@@ -18228,10 +18324,10 @@
         <v>131</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>132</v>
+        <v>5531</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>133</v>
+        <v>5523</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>134</v>
@@ -18945,7 +19041,7 @@
         <v>199</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>200</v>
+        <v>5532</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>201</v>
@@ -18987,7 +19083,7 @@
         <v>203</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>204</v>
+        <v>5533</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>205</v>
@@ -19029,7 +19125,7 @@
         <v>207</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>208</v>
+        <v>5534</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>209</v>
@@ -19071,7 +19167,7 @@
         <v>211</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>212</v>
+        <v>5535</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>213</v>
@@ -19113,7 +19209,7 @@
         <v>215</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>216</v>
+        <v>5536</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>217</v>
@@ -19155,7 +19251,7 @@
         <v>219</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>220</v>
+        <v>5537</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>221</v>
@@ -19197,7 +19293,7 @@
         <v>223</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>224</v>
+        <v>5538</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>225</v>
@@ -19239,7 +19335,7 @@
         <v>227</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>228</v>
+        <v>5539</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>229</v>
@@ -20622,7 +20718,7 @@
         <v>358</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>359</v>
+        <v>5540</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>360</v>
@@ -20664,7 +20760,7 @@
         <v>362</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>363</v>
+        <v>5541</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>364</v>
@@ -20706,7 +20802,7 @@
         <v>366</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>367</v>
+        <v>5542</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>368</v>
@@ -20748,7 +20844,7 @@
         <v>370</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>371</v>
+        <v>5543</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>372</v>
@@ -20790,7 +20886,7 @@
         <v>374</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>375</v>
+        <v>5544</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>376</v>
@@ -20832,7 +20928,7 @@
         <v>378</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>379</v>
+        <v>5545</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>380</v>
@@ -20874,7 +20970,7 @@
         <v>382</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>383</v>
+        <v>5546</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>384</v>
@@ -20916,7 +21012,7 @@
         <v>386</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>387</v>
+        <v>5547</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>388</v>
